--- a/htr-FHIR/ig/StructureDefinition-fr-core-service-event.xlsx
+++ b/htr-FHIR/ig/StructureDefinition-fr-core-service-event.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2998" uniqueCount="316">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2998" uniqueCount="315">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-24T12:52:51+00:00</t>
+    <t>2025-02-24T13:32:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -316,10 +316,6 @@
   </si>
   <si>
     <t>InfrastructureRoot.typeId</t>
-  </si>
-  <si>
-    <t xml:space="preserve">II-1:An II instance must have either a root or an nullFlavor. {root.exists() or nullFlavor.exists()}
-</t>
   </si>
   <si>
     <t>ServiceEvent.typeId.nullFlavor</t>
@@ -1875,7 +1871,7 @@
         <v>74</v>
       </c>
       <c r="AJ5" t="s" s="2">
-        <v>99</v>
+        <v>74</v>
       </c>
       <c r="AK5" t="s" s="2">
         <v>74</v>
@@ -1883,10 +1879,10 @@
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="C6" s="2"/>
       <c r="D6" t="s" s="2">
@@ -1984,39 +1980,39 @@
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="C7" s="2"/>
       <c r="D7" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E7" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="F7" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G7" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H7" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I7" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J7" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K7" t="s" s="2">
         <v>102</v>
-      </c>
-      <c r="F7" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G7" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="H7" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="I7" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="J7" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="K7" t="s" s="2">
-        <v>103</v>
       </c>
       <c r="L7" s="2"/>
       <c r="M7" t="s" s="2">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="N7" s="2"/>
       <c r="O7" s="2"/>
@@ -2067,7 +2063,7 @@
         <v>74</v>
       </c>
       <c r="AF7" t="s" s="2">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="AG7" t="s" s="2">
         <v>80</v>
@@ -2087,39 +2083,39 @@
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C8" s="2"/>
       <c r="D8" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E8" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="F8" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G8" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H8" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I8" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J8" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K8" t="s" s="2">
         <v>107</v>
-      </c>
-      <c r="F8" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G8" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="H8" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="I8" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="J8" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="K8" t="s" s="2">
-        <v>108</v>
       </c>
       <c r="L8" s="2"/>
       <c r="M8" t="s" s="2">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="N8" s="2"/>
       <c r="O8" s="2"/>
@@ -2170,7 +2166,7 @@
         <v>74</v>
       </c>
       <c r="AF8" t="s" s="2">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="AG8" t="s" s="2">
         <v>80</v>
@@ -2190,39 +2186,39 @@
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="C9" s="2"/>
       <c r="D9" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E9" t="s" s="2">
+        <v>111</v>
+      </c>
+      <c r="F9" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="G9" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="H9" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I9" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J9" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K9" t="s" s="2">
         <v>112</v>
-      </c>
-      <c r="F9" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="G9" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="H9" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="I9" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="J9" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="K9" t="s" s="2">
-        <v>113</v>
       </c>
       <c r="L9" s="2"/>
       <c r="M9" t="s" s="2">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="N9" s="2"/>
       <c r="O9" s="2"/>
@@ -2231,49 +2227,49 @@
       </c>
       <c r="Q9" s="2"/>
       <c r="R9" t="s" s="2">
+        <v>114</v>
+      </c>
+      <c r="S9" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="T9" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="U9" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="V9" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="W9" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="X9" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Y9" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Z9" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AA9" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB9" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC9" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD9" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE9" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF9" t="s" s="2">
         <v>115</v>
-      </c>
-      <c r="S9" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="T9" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="U9" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="V9" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="W9" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="X9" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Y9" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Z9" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AA9" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AB9" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AC9" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AD9" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AE9" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AF9" t="s" s="2">
-        <v>116</v>
       </c>
       <c r="AG9" t="s" s="2">
         <v>80</v>
@@ -2293,17 +2289,17 @@
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C10" s="2"/>
       <c r="D10" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E10" t="s" s="2">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="F10" t="s" s="2">
         <v>75</v>
@@ -2321,11 +2317,11 @@
         <v>74</v>
       </c>
       <c r="K10" t="s" s="2">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="L10" s="2"/>
       <c r="M10" t="s" s="2">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="N10" s="2"/>
       <c r="O10" s="2"/>
@@ -2376,7 +2372,7 @@
         <v>74</v>
       </c>
       <c r="AF10" t="s" s="2">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="AG10" t="s" s="2">
         <v>80</v>
@@ -2396,10 +2392,10 @@
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" t="s" s="2">
@@ -2426,7 +2422,7 @@
       </c>
       <c r="L11" s="2"/>
       <c r="M11" t="s" s="2">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="N11" s="2"/>
       <c r="O11" s="2"/>
@@ -2477,7 +2473,7 @@
         <v>74</v>
       </c>
       <c r="AF11" t="s" s="2">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="AG11" t="s" s="2">
         <v>80</v>
@@ -2497,10 +2493,10 @@
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" t="s" s="2">
@@ -2530,7 +2526,7 @@
       <c r="N12" s="2"/>
       <c r="O12" s="2"/>
       <c r="P12" t="s" s="2">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="Q12" s="2"/>
       <c r="R12" t="s" s="2">
@@ -2556,7 +2552,7 @@
       </c>
       <c r="Y12" s="2"/>
       <c r="Z12" t="s" s="2">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="AA12" t="s" s="2">
         <v>74</v>
@@ -2574,7 +2570,7 @@
         <v>74</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="AG12" t="s" s="2">
         <v>80</v>
@@ -2594,10 +2590,10 @@
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
@@ -2631,7 +2627,7 @@
       </c>
       <c r="Q13" s="2"/>
       <c r="R13" t="s" s="2">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="S13" t="s" s="2">
         <v>74</v>
@@ -2653,7 +2649,7 @@
       </c>
       <c r="Y13" s="2"/>
       <c r="Z13" t="s" s="2">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="AA13" t="s" s="2">
         <v>74</v>
@@ -2671,7 +2667,7 @@
         <v>74</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>80</v>
@@ -2691,10 +2687,10 @@
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
@@ -2720,7 +2716,7 @@
         <v>96</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="M14" s="2"/>
       <c r="N14" s="2"/>
@@ -2772,7 +2768,7 @@
         <v>74</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>80</v>
@@ -2792,10 +2788,10 @@
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
@@ -2818,13 +2814,13 @@
         <v>74</v>
       </c>
       <c r="K15" t="s" s="2">
+        <v>132</v>
+      </c>
+      <c r="L15" t="s" s="2">
         <v>133</v>
       </c>
-      <c r="L15" t="s" s="2">
+      <c r="M15" t="s" s="2">
         <v>134</v>
-      </c>
-      <c r="M15" t="s" s="2">
-        <v>135</v>
       </c>
       <c r="N15" s="2"/>
       <c r="O15" s="2"/>
@@ -2875,7 +2871,7 @@
         <v>74</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>80</v>
@@ -2895,10 +2891,10 @@
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
@@ -2996,10 +2992,10 @@
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -3027,10 +3023,10 @@
         <v>86</v>
       </c>
       <c r="L17" t="s" s="2">
+        <v>137</v>
+      </c>
+      <c r="M17" t="s" s="2">
         <v>138</v>
-      </c>
-      <c r="M17" t="s" s="2">
-        <v>139</v>
       </c>
       <c r="N17" s="2"/>
       <c r="O17" s="2"/>
@@ -3081,7 +3077,7 @@
         <v>74</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>80</v>
@@ -3101,17 +3097,17 @@
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E18" t="s" s="2">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="F18" t="s" s="2">
         <v>75</v>
@@ -3129,11 +3125,11 @@
         <v>74</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="L18" s="2"/>
       <c r="M18" t="s" s="2">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="N18" s="2"/>
       <c r="O18" s="2"/>
@@ -3184,7 +3180,7 @@
         <v>74</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>80</v>
@@ -3204,17 +3200,17 @@
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E19" t="s" s="2">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="F19" t="s" s="2">
         <v>80</v>
@@ -3232,11 +3228,11 @@
         <v>74</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="L19" s="2"/>
       <c r="M19" t="s" s="2">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="N19" s="2"/>
       <c r="O19" s="2"/>
@@ -3287,7 +3283,7 @@
         <v>74</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>80</v>
@@ -3307,17 +3303,17 @@
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E20" t="s" s="2">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="F20" t="s" s="2">
         <v>80</v>
@@ -3335,11 +3331,11 @@
         <v>74</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="L20" s="2"/>
       <c r="M20" t="s" s="2">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="N20" s="2"/>
       <c r="O20" s="2"/>
@@ -3390,7 +3386,7 @@
         <v>74</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>80</v>
@@ -3410,17 +3406,17 @@
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E21" t="s" s="2">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="F21" t="s" s="2">
         <v>75</v>
@@ -3438,11 +3434,11 @@
         <v>74</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="L21" s="2"/>
       <c r="M21" t="s" s="2">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="N21" s="2"/>
       <c r="O21" s="2"/>
@@ -3493,7 +3489,7 @@
         <v>74</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>80</v>
@@ -3513,10 +3509,10 @@
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -3539,11 +3535,11 @@
         <v>74</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="L22" s="2"/>
       <c r="M22" t="s" s="2">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="N22" s="2"/>
       <c r="O22" s="2"/>
@@ -3594,7 +3590,7 @@
         <v>74</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>80</v>
@@ -3614,10 +3610,10 @@
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -3640,11 +3636,11 @@
         <v>74</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="L23" s="2"/>
       <c r="M23" t="s" s="2">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="N23" s="2"/>
       <c r="O23" s="2"/>
@@ -3695,7 +3691,7 @@
         <v>74</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>80</v>
@@ -3715,39 +3711,39 @@
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E24" t="s" s="2">
+        <v>164</v>
+      </c>
+      <c r="F24" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G24" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="H24" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I24" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J24" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K24" t="s" s="2">
         <v>165</v>
-      </c>
-      <c r="F24" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G24" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="H24" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="I24" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="J24" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="K24" t="s" s="2">
-        <v>166</v>
       </c>
       <c r="L24" s="2"/>
       <c r="M24" t="s" s="2">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="N24" s="2"/>
       <c r="O24" s="2"/>
@@ -3798,7 +3794,7 @@
         <v>74</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>80</v>
@@ -3818,39 +3814,39 @@
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E25" t="s" s="2">
+        <v>169</v>
+      </c>
+      <c r="F25" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G25" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H25" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I25" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J25" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K25" t="s" s="2">
         <v>170</v>
-      </c>
-      <c r="F25" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G25" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="H25" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="I25" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="J25" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="K25" t="s" s="2">
-        <v>171</v>
       </c>
       <c r="L25" s="2"/>
       <c r="M25" t="s" s="2">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="N25" s="2"/>
       <c r="O25" s="2"/>
@@ -3901,7 +3897,7 @@
         <v>74</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>80</v>
@@ -3921,17 +3917,17 @@
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E26" t="s" s="2">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="F26" t="s" s="2">
         <v>80</v>
@@ -3949,13 +3945,13 @@
         <v>74</v>
       </c>
       <c r="K26" t="s" s="2">
+        <v>175</v>
+      </c>
+      <c r="L26" t="s" s="2">
         <v>176</v>
       </c>
-      <c r="L26" t="s" s="2">
+      <c r="M26" t="s" s="2">
         <v>177</v>
-      </c>
-      <c r="M26" t="s" s="2">
-        <v>178</v>
       </c>
       <c r="N26" s="2"/>
       <c r="O26" s="2"/>
@@ -4006,7 +4002,7 @@
         <v>74</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>80</v>
@@ -4026,10 +4022,10 @@
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -4127,10 +4123,10 @@
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -4159,7 +4155,7 @@
       </c>
       <c r="L28" s="2"/>
       <c r="M28" t="s" s="2">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="N28" s="2"/>
       <c r="O28" s="2"/>
@@ -4210,7 +4206,7 @@
         <v>74</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>80</v>
@@ -4230,17 +4226,17 @@
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E29" t="s" s="2">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="F29" t="s" s="2">
         <v>80</v>
@@ -4258,11 +4254,11 @@
         <v>74</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="L29" s="2"/>
       <c r="M29" t="s" s="2">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="N29" s="2"/>
       <c r="O29" s="2"/>
@@ -4313,7 +4309,7 @@
         <v>74</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>80</v>
@@ -4333,17 +4329,17 @@
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E30" t="s" s="2">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="F30" t="s" s="2">
         <v>80</v>
@@ -4361,11 +4357,11 @@
         <v>74</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="L30" s="2"/>
       <c r="M30" t="s" s="2">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="N30" s="2"/>
       <c r="O30" s="2"/>
@@ -4416,7 +4412,7 @@
         <v>74</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>80</v>
@@ -4436,17 +4432,17 @@
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E31" t="s" s="2">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="F31" t="s" s="2">
         <v>80</v>
@@ -4464,11 +4460,11 @@
         <v>74</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="L31" s="2"/>
       <c r="M31" t="s" s="2">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="N31" s="2"/>
       <c r="O31" s="2"/>
@@ -4519,7 +4515,7 @@
         <v>74</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>80</v>
@@ -4539,17 +4535,17 @@
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E32" t="s" s="2">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="F32" t="s" s="2">
         <v>80</v>
@@ -4567,11 +4563,11 @@
         <v>74</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="L32" s="2"/>
       <c r="M32" t="s" s="2">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="N32" s="2"/>
       <c r="O32" s="2"/>
@@ -4622,7 +4618,7 @@
         <v>74</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>80</v>
@@ -4642,10 +4638,10 @@
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -4668,11 +4664,11 @@
         <v>74</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="L33" s="2"/>
       <c r="M33" t="s" s="2">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="N33" s="2"/>
       <c r="O33" s="2"/>
@@ -4723,7 +4719,7 @@
         <v>74</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>80</v>
@@ -4743,10 +4739,10 @@
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -4769,11 +4765,11 @@
         <v>74</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="L34" s="2"/>
       <c r="M34" t="s" s="2">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="N34" s="2"/>
       <c r="O34" s="2"/>
@@ -4824,7 +4820,7 @@
         <v>74</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>80</v>
@@ -4844,39 +4840,39 @@
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E35" t="s" s="2">
+        <v>164</v>
+      </c>
+      <c r="F35" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G35" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="H35" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I35" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J35" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K35" t="s" s="2">
         <v>165</v>
-      </c>
-      <c r="F35" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G35" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="H35" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="I35" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="J35" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="K35" t="s" s="2">
-        <v>166</v>
       </c>
       <c r="L35" s="2"/>
       <c r="M35" t="s" s="2">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="N35" s="2"/>
       <c r="O35" s="2"/>
@@ -4927,7 +4923,7 @@
         <v>74</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>80</v>
@@ -4947,17 +4943,17 @@
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E36" t="s" s="2">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="F36" t="s" s="2">
         <v>80</v>
@@ -4975,13 +4971,13 @@
         <v>74</v>
       </c>
       <c r="K36" t="s" s="2">
+        <v>170</v>
+      </c>
+      <c r="L36" t="s" s="2">
+        <v>189</v>
+      </c>
+      <c r="M36" t="s" s="2">
         <v>171</v>
-      </c>
-      <c r="L36" t="s" s="2">
-        <v>190</v>
-      </c>
-      <c r="M36" t="s" s="2">
-        <v>172</v>
       </c>
       <c r="N36" s="2"/>
       <c r="O36" s="2"/>
@@ -5032,7 +5028,7 @@
         <v>74</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>80</v>
@@ -5052,17 +5048,17 @@
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E37" t="s" s="2">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="F37" t="s" s="2">
         <v>80</v>
@@ -5080,11 +5076,11 @@
         <v>74</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="L37" s="2"/>
       <c r="M37" t="s" s="2">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="N37" s="2"/>
       <c r="O37" s="2"/>
@@ -5135,7 +5131,7 @@
         <v>74</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>80</v>
@@ -5155,10 +5151,10 @@
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -5181,10 +5177,10 @@
         <v>74</v>
       </c>
       <c r="K38" t="s" s="2">
+        <v>192</v>
+      </c>
+      <c r="L38" t="s" s="2">
         <v>193</v>
-      </c>
-      <c r="L38" t="s" s="2">
-        <v>194</v>
       </c>
       <c r="M38" s="2"/>
       <c r="N38" s="2"/>
@@ -5236,7 +5232,7 @@
         <v>74</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>80</v>
@@ -5256,10 +5252,10 @@
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -5357,10 +5353,10 @@
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -5383,11 +5379,11 @@
         <v>74</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="L40" s="2"/>
       <c r="M40" t="s" s="2">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="N40" s="2"/>
       <c r="O40" s="2"/>
@@ -5438,7 +5434,7 @@
         <v>74</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>80</v>
@@ -5458,10 +5454,10 @@
     </row>
     <row r="41">
       <c r="A41" t="s" s="2">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -5488,12 +5484,12 @@
       </c>
       <c r="L41" s="2"/>
       <c r="M41" t="s" s="2">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="N41" s="2"/>
       <c r="O41" s="2"/>
       <c r="P41" t="s" s="2">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="Q41" s="2"/>
       <c r="R41" t="s" s="2">
@@ -5519,25 +5515,25 @@
       </c>
       <c r="Y41" s="2"/>
       <c r="Z41" t="s" s="2">
+        <v>202</v>
+      </c>
+      <c r="AA41" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB41" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC41" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD41" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE41" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF41" t="s" s="2">
         <v>203</v>
-      </c>
-      <c r="AA41" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AB41" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AC41" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AD41" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AE41" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AF41" t="s" s="2">
-        <v>204</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>80</v>
@@ -5557,41 +5553,41 @@
     </row>
     <row r="42">
       <c r="A42" t="s" s="2">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E42" t="s" s="2">
+        <v>205</v>
+      </c>
+      <c r="F42" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="G42" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="H42" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I42" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J42" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K42" t="s" s="2">
         <v>206</v>
       </c>
-      <c r="F42" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="G42" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="H42" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="I42" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="J42" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="K42" t="s" s="2">
+      <c r="L42" t="s" s="2">
         <v>207</v>
       </c>
-      <c r="L42" t="s" s="2">
+      <c r="M42" t="s" s="2">
         <v>208</v>
-      </c>
-      <c r="M42" t="s" s="2">
-        <v>209</v>
       </c>
       <c r="N42" s="2"/>
       <c r="O42" s="2"/>
@@ -5642,7 +5638,7 @@
         <v>74</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>80</v>
@@ -5662,39 +5658,39 @@
     </row>
     <row r="43">
       <c r="A43" t="s" s="2">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E43" t="s" s="2">
+        <v>211</v>
+      </c>
+      <c r="F43" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G43" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H43" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I43" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J43" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K43" t="s" s="2">
         <v>212</v>
-      </c>
-      <c r="F43" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G43" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="H43" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="I43" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="J43" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="K43" t="s" s="2">
-        <v>213</v>
       </c>
       <c r="L43" s="2"/>
       <c r="M43" t="s" s="2">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="N43" s="2"/>
       <c r="O43" s="2"/>
@@ -5745,7 +5741,7 @@
         <v>74</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>80</v>
@@ -5765,39 +5761,39 @@
     </row>
     <row r="44">
       <c r="A44" t="s" s="2">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E44" t="s" s="2">
+        <v>216</v>
+      </c>
+      <c r="F44" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G44" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H44" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I44" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J44" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K44" t="s" s="2">
         <v>217</v>
-      </c>
-      <c r="F44" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G44" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="H44" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="I44" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="J44" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="K44" t="s" s="2">
-        <v>218</v>
       </c>
       <c r="L44" s="2"/>
       <c r="M44" t="s" s="2">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="N44" s="2"/>
       <c r="O44" s="2"/>
@@ -5848,7 +5844,7 @@
         <v>74</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>80</v>
@@ -5868,41 +5864,41 @@
     </row>
     <row r="45">
       <c r="A45" t="s" s="2">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E45" t="s" s="2">
+        <v>221</v>
+      </c>
+      <c r="F45" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G45" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="H45" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I45" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J45" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K45" t="s" s="2">
+        <v>206</v>
+      </c>
+      <c r="L45" t="s" s="2">
         <v>222</v>
       </c>
-      <c r="F45" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G45" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="H45" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="I45" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="J45" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="K45" t="s" s="2">
-        <v>207</v>
-      </c>
-      <c r="L45" t="s" s="2">
+      <c r="M45" t="s" s="2">
         <v>223</v>
-      </c>
-      <c r="M45" t="s" s="2">
-        <v>224</v>
       </c>
       <c r="N45" s="2"/>
       <c r="O45" s="2"/>
@@ -5953,7 +5949,7 @@
         <v>74</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>80</v>
@@ -5973,10 +5969,10 @@
     </row>
     <row r="46">
       <c r="A46" t="s" s="2">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -5999,10 +5995,10 @@
         <v>74</v>
       </c>
       <c r="K46" t="s" s="2">
+        <v>226</v>
+      </c>
+      <c r="L46" t="s" s="2">
         <v>227</v>
-      </c>
-      <c r="L46" t="s" s="2">
-        <v>228</v>
       </c>
       <c r="M46" s="2"/>
       <c r="N46" s="2"/>
@@ -6054,7 +6050,7 @@
         <v>74</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>80</v>
@@ -6074,10 +6070,10 @@
     </row>
     <row r="47">
       <c r="A47" t="s" s="2">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -6175,10 +6171,10 @@
     </row>
     <row r="48">
       <c r="A48" t="s" s="2">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -6276,10 +6272,10 @@
     </row>
     <row r="49">
       <c r="A49" t="s" s="2">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -6369,7 +6365,7 @@
         <v>74</v>
       </c>
       <c r="AJ49" t="s" s="2">
-        <v>99</v>
+        <v>74</v>
       </c>
       <c r="AK49" t="s" s="2">
         <v>74</v>
@@ -6377,10 +6373,10 @@
     </row>
     <row r="50">
       <c r="A50" t="s" s="2">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -6478,39 +6474,39 @@
     </row>
     <row r="51">
       <c r="A51" t="s" s="2">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E51" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="F51" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G51" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H51" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I51" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J51" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K51" t="s" s="2">
         <v>102</v>
-      </c>
-      <c r="F51" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G51" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="H51" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="I51" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="J51" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="K51" t="s" s="2">
-        <v>103</v>
       </c>
       <c r="L51" s="2"/>
       <c r="M51" t="s" s="2">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="N51" s="2"/>
       <c r="O51" s="2"/>
@@ -6561,7 +6557,7 @@
         <v>74</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>80</v>
@@ -6581,39 +6577,39 @@
     </row>
     <row r="52">
       <c r="A52" t="s" s="2">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E52" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="F52" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G52" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H52" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I52" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J52" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K52" t="s" s="2">
         <v>107</v>
-      </c>
-      <c r="F52" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G52" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="H52" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="I52" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="J52" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="K52" t="s" s="2">
-        <v>108</v>
       </c>
       <c r="L52" s="2"/>
       <c r="M52" t="s" s="2">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="N52" s="2"/>
       <c r="O52" s="2"/>
@@ -6664,7 +6660,7 @@
         <v>74</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>80</v>
@@ -6684,39 +6680,39 @@
     </row>
     <row r="53">
       <c r="A53" t="s" s="2">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E53" t="s" s="2">
+        <v>111</v>
+      </c>
+      <c r="F53" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="G53" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="H53" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I53" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J53" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K53" t="s" s="2">
         <v>112</v>
-      </c>
-      <c r="F53" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="G53" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="H53" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="I53" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="J53" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="K53" t="s" s="2">
-        <v>113</v>
       </c>
       <c r="L53" s="2"/>
       <c r="M53" t="s" s="2">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="N53" s="2"/>
       <c r="O53" s="2"/>
@@ -6725,49 +6721,49 @@
       </c>
       <c r="Q53" s="2"/>
       <c r="R53" t="s" s="2">
+        <v>114</v>
+      </c>
+      <c r="S53" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="T53" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="U53" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="V53" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="W53" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="X53" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Y53" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Z53" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AA53" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB53" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC53" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD53" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE53" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF53" t="s" s="2">
         <v>115</v>
-      </c>
-      <c r="S53" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="T53" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="U53" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="V53" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="W53" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="X53" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Y53" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Z53" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AA53" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AB53" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AC53" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AD53" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AE53" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AF53" t="s" s="2">
-        <v>116</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>80</v>
@@ -6787,17 +6783,17 @@
     </row>
     <row r="54">
       <c r="A54" t="s" s="2">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E54" t="s" s="2">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="F54" t="s" s="2">
         <v>75</v>
@@ -6815,11 +6811,11 @@
         <v>74</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="L54" s="2"/>
       <c r="M54" t="s" s="2">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="N54" s="2"/>
       <c r="O54" s="2"/>
@@ -6870,7 +6866,7 @@
         <v>74</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>80</v>
@@ -6890,10 +6886,10 @@
     </row>
     <row r="55">
       <c r="A55" t="s" s="2">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -6920,7 +6916,7 @@
       </c>
       <c r="L55" s="2"/>
       <c r="M55" t="s" s="2">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="N55" s="2"/>
       <c r="O55" s="2"/>
@@ -6971,7 +6967,7 @@
         <v>74</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>80</v>
@@ -6991,10 +6987,10 @@
     </row>
     <row r="56">
       <c r="A56" t="s" s="2">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -7020,7 +7016,7 @@
         <v>86</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="M56" s="2"/>
       <c r="N56" s="2"/>
@@ -7033,7 +7029,7 @@
         <v>74</v>
       </c>
       <c r="S56" t="s" s="2">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="T56" t="s" s="2">
         <v>74</v>
@@ -7052,25 +7048,25 @@
       </c>
       <c r="Y56" s="2"/>
       <c r="Z56" t="s" s="2">
+        <v>240</v>
+      </c>
+      <c r="AA56" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB56" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC56" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD56" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE56" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF56" t="s" s="2">
         <v>241</v>
-      </c>
-      <c r="AA56" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AB56" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AC56" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AD56" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AE56" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AF56" t="s" s="2">
-        <v>242</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>75</v>
@@ -7090,10 +7086,10 @@
     </row>
     <row r="57">
       <c r="A57" t="s" s="2">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -7116,10 +7112,10 @@
         <v>74</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="M57" s="2"/>
       <c r="N57" s="2"/>
@@ -7171,7 +7167,7 @@
         <v>74</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>80</v>
@@ -7191,10 +7187,10 @@
     </row>
     <row r="58">
       <c r="A58" t="s" s="2">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -7217,10 +7213,10 @@
         <v>74</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="M58" s="2"/>
       <c r="N58" s="2"/>
@@ -7272,7 +7268,7 @@
         <v>74</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>80</v>
@@ -7292,10 +7288,10 @@
     </row>
     <row r="59">
       <c r="A59" t="s" s="2">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -7318,10 +7314,10 @@
         <v>74</v>
       </c>
       <c r="K59" t="s" s="2">
+        <v>249</v>
+      </c>
+      <c r="L59" t="s" s="2">
         <v>250</v>
-      </c>
-      <c r="L59" t="s" s="2">
-        <v>251</v>
       </c>
       <c r="M59" s="2"/>
       <c r="N59" s="2"/>
@@ -7373,7 +7369,7 @@
         <v>74</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>75</v>
@@ -7393,10 +7389,10 @@
     </row>
     <row r="60">
       <c r="A60" t="s" s="2">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -7494,10 +7490,10 @@
     </row>
     <row r="61">
       <c r="A61" t="s" s="2">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -7595,10 +7591,10 @@
     </row>
     <row r="62">
       <c r="A62" t="s" s="2">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -7688,7 +7684,7 @@
         <v>74</v>
       </c>
       <c r="AJ62" t="s" s="2">
-        <v>99</v>
+        <v>74</v>
       </c>
       <c r="AK62" t="s" s="2">
         <v>74</v>
@@ -7696,10 +7692,10 @@
     </row>
     <row r="63">
       <c r="A63" t="s" s="2">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -7797,39 +7793,39 @@
     </row>
     <row r="64">
       <c r="A64" t="s" s="2">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E64" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="F64" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G64" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H64" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I64" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J64" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K64" t="s" s="2">
         <v>102</v>
-      </c>
-      <c r="F64" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G64" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="H64" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="I64" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="J64" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="K64" t="s" s="2">
-        <v>103</v>
       </c>
       <c r="L64" s="2"/>
       <c r="M64" t="s" s="2">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="N64" s="2"/>
       <c r="O64" s="2"/>
@@ -7880,7 +7876,7 @@
         <v>74</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>80</v>
@@ -7900,39 +7896,39 @@
     </row>
     <row r="65">
       <c r="A65" t="s" s="2">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E65" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="F65" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G65" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H65" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I65" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J65" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K65" t="s" s="2">
         <v>107</v>
-      </c>
-      <c r="F65" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G65" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="H65" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="I65" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="J65" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="K65" t="s" s="2">
-        <v>108</v>
       </c>
       <c r="L65" s="2"/>
       <c r="M65" t="s" s="2">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="N65" s="2"/>
       <c r="O65" s="2"/>
@@ -7983,7 +7979,7 @@
         <v>74</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>80</v>
@@ -8003,39 +7999,39 @@
     </row>
     <row r="66">
       <c r="A66" t="s" s="2">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E66" t="s" s="2">
+        <v>111</v>
+      </c>
+      <c r="F66" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="G66" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="H66" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I66" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J66" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K66" t="s" s="2">
         <v>112</v>
-      </c>
-      <c r="F66" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="G66" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="H66" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="I66" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="J66" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="K66" t="s" s="2">
-        <v>113</v>
       </c>
       <c r="L66" s="2"/>
       <c r="M66" t="s" s="2">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="N66" s="2"/>
       <c r="O66" s="2"/>
@@ -8044,49 +8040,49 @@
       </c>
       <c r="Q66" s="2"/>
       <c r="R66" t="s" s="2">
+        <v>114</v>
+      </c>
+      <c r="S66" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="T66" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="U66" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="V66" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="W66" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="X66" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Y66" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Z66" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AA66" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB66" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC66" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD66" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE66" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF66" t="s" s="2">
         <v>115</v>
-      </c>
-      <c r="S66" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="T66" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="U66" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="V66" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="W66" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="X66" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Y66" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Z66" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AA66" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AB66" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AC66" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AD66" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AE66" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AF66" t="s" s="2">
-        <v>116</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>80</v>
@@ -8106,17 +8102,17 @@
     </row>
     <row r="67">
       <c r="A67" t="s" s="2">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E67" t="s" s="2">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="F67" t="s" s="2">
         <v>75</v>
@@ -8134,11 +8130,11 @@
         <v>74</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="L67" s="2"/>
       <c r="M67" t="s" s="2">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="N67" s="2"/>
       <c r="O67" s="2"/>
@@ -8189,7 +8185,7 @@
         <v>74</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>80</v>
@@ -8209,10 +8205,10 @@
     </row>
     <row r="68">
       <c r="A68" t="s" s="2">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -8239,7 +8235,7 @@
       </c>
       <c r="L68" s="2"/>
       <c r="M68" t="s" s="2">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="N68" s="2"/>
       <c r="O68" s="2"/>
@@ -8290,7 +8286,7 @@
         <v>74</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>80</v>
@@ -8310,10 +8306,10 @@
     </row>
     <row r="69">
       <c r="A69" t="s" s="2">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -8347,7 +8343,7 @@
       </c>
       <c r="Q69" s="2"/>
       <c r="R69" t="s" s="2">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="S69" t="s" s="2">
         <v>74</v>
@@ -8369,25 +8365,25 @@
       </c>
       <c r="Y69" s="2"/>
       <c r="Z69" t="s" s="2">
+        <v>263</v>
+      </c>
+      <c r="AA69" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB69" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC69" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD69" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE69" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF69" t="s" s="2">
         <v>264</v>
-      </c>
-      <c r="AA69" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AB69" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AC69" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AD69" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AE69" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AF69" t="s" s="2">
-        <v>265</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>80</v>
@@ -8407,10 +8403,10 @@
     </row>
     <row r="70">
       <c r="A70" t="s" s="2">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -8436,7 +8432,7 @@
         <v>96</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="M70" s="2"/>
       <c r="N70" s="2"/>
@@ -8488,7 +8484,7 @@
         <v>74</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>75</v>
@@ -8508,10 +8504,10 @@
     </row>
     <row r="71">
       <c r="A71" t="s" s="2">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -8609,39 +8605,39 @@
     </row>
     <row r="72">
       <c r="A72" t="s" s="2">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E72" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="F72" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G72" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H72" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I72" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J72" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K72" t="s" s="2">
         <v>102</v>
-      </c>
-      <c r="F72" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G72" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="H72" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="I72" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="J72" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="K72" t="s" s="2">
-        <v>103</v>
       </c>
       <c r="L72" s="2"/>
       <c r="M72" t="s" s="2">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="N72" s="2"/>
       <c r="O72" s="2"/>
@@ -8692,7 +8688,7 @@
         <v>74</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>80</v>
@@ -8712,39 +8708,39 @@
     </row>
     <row r="73">
       <c r="A73" t="s" s="2">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E73" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="F73" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G73" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H73" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I73" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J73" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K73" t="s" s="2">
         <v>107</v>
-      </c>
-      <c r="F73" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G73" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="H73" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="I73" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="J73" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="K73" t="s" s="2">
-        <v>108</v>
       </c>
       <c r="L73" s="2"/>
       <c r="M73" t="s" s="2">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="N73" s="2"/>
       <c r="O73" s="2"/>
@@ -8795,7 +8791,7 @@
         <v>74</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>80</v>
@@ -8815,41 +8811,41 @@
     </row>
     <row r="74">
       <c r="A74" t="s" s="2">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E74" t="s" s="2">
+        <v>111</v>
+      </c>
+      <c r="F74" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="G74" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="H74" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I74" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J74" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K74" t="s" s="2">
         <v>112</v>
       </c>
-      <c r="F74" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="G74" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="H74" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="I74" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="J74" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="K74" t="s" s="2">
-        <v>113</v>
-      </c>
       <c r="L74" t="s" s="2">
+        <v>272</v>
+      </c>
+      <c r="M74" t="s" s="2">
         <v>273</v>
-      </c>
-      <c r="M74" t="s" s="2">
-        <v>274</v>
       </c>
       <c r="N74" s="2"/>
       <c r="O74" s="2"/>
@@ -8900,7 +8896,7 @@
         <v>74</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>80</v>
@@ -8920,41 +8916,41 @@
     </row>
     <row r="75">
       <c r="A75" t="s" s="2">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E75" t="s" s="2">
+        <v>117</v>
+      </c>
+      <c r="F75" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="G75" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="H75" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I75" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J75" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K75" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="L75" t="s" s="2">
+        <v>275</v>
+      </c>
+      <c r="M75" t="s" s="2">
         <v>118</v>
-      </c>
-      <c r="F75" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="G75" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="H75" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="I75" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="J75" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="K75" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="L75" t="s" s="2">
-        <v>276</v>
-      </c>
-      <c r="M75" t="s" s="2">
-        <v>119</v>
       </c>
       <c r="N75" s="2"/>
       <c r="O75" s="2"/>
@@ -9005,7 +9001,7 @@
         <v>74</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>80</v>
@@ -9025,10 +9021,10 @@
     </row>
     <row r="76">
       <c r="A76" t="s" s="2">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -9051,7 +9047,7 @@
         <v>74</v>
       </c>
       <c r="K76" t="s" s="2">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="L76" s="2"/>
       <c r="M76" s="2"/>
@@ -9104,7 +9100,7 @@
         <v>74</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>80</v>
@@ -9124,10 +9120,10 @@
     </row>
     <row r="77">
       <c r="A77" t="s" s="2">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -9150,10 +9146,10 @@
         <v>74</v>
       </c>
       <c r="K77" t="s" s="2">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="M77" s="2"/>
       <c r="N77" s="2"/>
@@ -9185,25 +9181,25 @@
       </c>
       <c r="Y77" s="2"/>
       <c r="Z77" t="s" s="2">
+        <v>281</v>
+      </c>
+      <c r="AA77" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB77" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC77" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD77" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE77" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF77" t="s" s="2">
         <v>282</v>
-      </c>
-      <c r="AA77" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AB77" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AC77" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AD77" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AE77" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AF77" t="s" s="2">
-        <v>283</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>80</v>
@@ -9223,10 +9219,10 @@
     </row>
     <row r="78">
       <c r="A78" t="s" s="2">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -9324,10 +9320,10 @@
     </row>
     <row r="79">
       <c r="A79" t="s" s="2">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -9356,7 +9352,7 @@
       </c>
       <c r="L79" s="2"/>
       <c r="M79" t="s" s="2">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="N79" s="2"/>
       <c r="O79" s="2"/>
@@ -9407,7 +9403,7 @@
         <v>74</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>80</v>
@@ -9427,17 +9423,17 @@
     </row>
     <row r="80">
       <c r="A80" t="s" s="2">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E80" t="s" s="2">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="F80" t="s" s="2">
         <v>80</v>
@@ -9455,11 +9451,11 @@
         <v>74</v>
       </c>
       <c r="K80" t="s" s="2">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="L80" s="2"/>
       <c r="M80" t="s" s="2">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="N80" s="2"/>
       <c r="O80" s="2"/>
@@ -9510,7 +9506,7 @@
         <v>74</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>80</v>
@@ -9530,17 +9526,17 @@
     </row>
     <row r="81">
       <c r="A81" t="s" s="2">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E81" t="s" s="2">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="F81" t="s" s="2">
         <v>80</v>
@@ -9558,11 +9554,11 @@
         <v>74</v>
       </c>
       <c r="K81" t="s" s="2">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="L81" s="2"/>
       <c r="M81" t="s" s="2">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="N81" s="2"/>
       <c r="O81" s="2"/>
@@ -9613,7 +9609,7 @@
         <v>74</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>80</v>
@@ -9633,17 +9629,17 @@
     </row>
     <row r="82">
       <c r="A82" t="s" s="2">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E82" t="s" s="2">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="F82" t="s" s="2">
         <v>80</v>
@@ -9661,11 +9657,11 @@
         <v>74</v>
       </c>
       <c r="K82" t="s" s="2">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="L82" s="2"/>
       <c r="M82" t="s" s="2">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="N82" s="2"/>
       <c r="O82" s="2"/>
@@ -9716,7 +9712,7 @@
         <v>74</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>80</v>
@@ -9736,17 +9732,17 @@
     </row>
     <row r="83">
       <c r="A83" t="s" s="2">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E83" t="s" s="2">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="F83" t="s" s="2">
         <v>80</v>
@@ -9764,11 +9760,11 @@
         <v>74</v>
       </c>
       <c r="K83" t="s" s="2">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="L83" s="2"/>
       <c r="M83" t="s" s="2">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="N83" s="2"/>
       <c r="O83" s="2"/>
@@ -9819,7 +9815,7 @@
         <v>74</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>80</v>
@@ -9839,10 +9835,10 @@
     </row>
     <row r="84">
       <c r="A84" t="s" s="2">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -9865,11 +9861,11 @@
         <v>74</v>
       </c>
       <c r="K84" t="s" s="2">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="L84" s="2"/>
       <c r="M84" t="s" s="2">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="N84" s="2"/>
       <c r="O84" s="2"/>
@@ -9920,7 +9916,7 @@
         <v>74</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>80</v>
@@ -9940,10 +9936,10 @@
     </row>
     <row r="85">
       <c r="A85" t="s" s="2">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -9966,11 +9962,11 @@
         <v>74</v>
       </c>
       <c r="K85" t="s" s="2">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="L85" s="2"/>
       <c r="M85" t="s" s="2">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="N85" s="2"/>
       <c r="O85" s="2"/>
@@ -10021,7 +10017,7 @@
         <v>74</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>80</v>
@@ -10041,39 +10037,39 @@
     </row>
     <row r="86">
       <c r="A86" t="s" s="2">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E86" t="s" s="2">
+        <v>164</v>
+      </c>
+      <c r="F86" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G86" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="H86" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I86" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J86" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K86" t="s" s="2">
         <v>165</v>
-      </c>
-      <c r="F86" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G86" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="H86" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="I86" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="J86" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="K86" t="s" s="2">
-        <v>166</v>
       </c>
       <c r="L86" s="2"/>
       <c r="M86" t="s" s="2">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="N86" s="2"/>
       <c r="O86" s="2"/>
@@ -10124,7 +10120,7 @@
         <v>74</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>80</v>
@@ -10144,39 +10140,39 @@
     </row>
     <row r="87">
       <c r="A87" t="s" s="2">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E87" t="s" s="2">
+        <v>169</v>
+      </c>
+      <c r="F87" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G87" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H87" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I87" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J87" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K87" t="s" s="2">
         <v>170</v>
-      </c>
-      <c r="F87" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="G87" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="H87" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="I87" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="J87" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="K87" t="s" s="2">
-        <v>171</v>
       </c>
       <c r="L87" s="2"/>
       <c r="M87" t="s" s="2">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="N87" s="2"/>
       <c r="O87" s="2"/>
@@ -10227,7 +10223,7 @@
         <v>74</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="AG87" t="s" s="2">
         <v>80</v>
@@ -10247,17 +10243,17 @@
     </row>
     <row r="88">
       <c r="A88" t="s" s="2">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E88" t="s" s="2">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="F88" t="s" s="2">
         <v>80</v>
@@ -10275,11 +10271,11 @@
         <v>74</v>
       </c>
       <c r="K88" t="s" s="2">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="L88" s="2"/>
       <c r="M88" t="s" s="2">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="N88" s="2"/>
       <c r="O88" s="2"/>
@@ -10330,7 +10326,7 @@
         <v>74</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>80</v>
@@ -10350,10 +10346,10 @@
     </row>
     <row r="89">
       <c r="A89" t="s" s="2">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -10376,10 +10372,10 @@
         <v>74</v>
       </c>
       <c r="K89" t="s" s="2">
+        <v>295</v>
+      </c>
+      <c r="L89" t="s" s="2">
         <v>296</v>
-      </c>
-      <c r="L89" t="s" s="2">
-        <v>297</v>
       </c>
       <c r="M89" s="2"/>
       <c r="N89" s="2"/>
@@ -10431,7 +10427,7 @@
         <v>74</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="AG89" t="s" s="2">
         <v>80</v>
@@ -10451,10 +10447,10 @@
     </row>
     <row r="90">
       <c r="A90" t="s" s="2">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -10477,10 +10473,10 @@
         <v>74</v>
       </c>
       <c r="K90" t="s" s="2">
+        <v>299</v>
+      </c>
+      <c r="L90" t="s" s="2">
         <v>300</v>
-      </c>
-      <c r="L90" t="s" s="2">
-        <v>301</v>
       </c>
       <c r="M90" s="2"/>
       <c r="N90" s="2"/>
@@ -10532,7 +10528,7 @@
         <v>74</v>
       </c>
       <c r="AF90" t="s" s="2">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="AG90" t="s" s="2">
         <v>80</v>
@@ -10552,10 +10548,10 @@
     </row>
     <row r="91">
       <c r="A91" t="s" s="2">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -10578,10 +10574,10 @@
         <v>74</v>
       </c>
       <c r="K91" t="s" s="2">
+        <v>303</v>
+      </c>
+      <c r="L91" t="s" s="2">
         <v>304</v>
-      </c>
-      <c r="L91" t="s" s="2">
-        <v>305</v>
       </c>
       <c r="M91" s="2"/>
       <c r="N91" s="2"/>
@@ -10633,7 +10629,7 @@
         <v>74</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="AG91" t="s" s="2">
         <v>80</v>
@@ -10653,10 +10649,10 @@
     </row>
     <row r="92">
       <c r="A92" t="s" s="2">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -10679,10 +10675,10 @@
         <v>74</v>
       </c>
       <c r="K92" t="s" s="2">
+        <v>307</v>
+      </c>
+      <c r="L92" t="s" s="2">
         <v>308</v>
-      </c>
-      <c r="L92" t="s" s="2">
-        <v>309</v>
       </c>
       <c r="M92" s="2"/>
       <c r="N92" s="2"/>
@@ -10734,7 +10730,7 @@
         <v>74</v>
       </c>
       <c r="AF92" t="s" s="2">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="AG92" t="s" s="2">
         <v>80</v>
@@ -10754,10 +10750,10 @@
     </row>
     <row r="93">
       <c r="A93" t="s" s="2">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -10780,7 +10776,7 @@
         <v>74</v>
       </c>
       <c r="K93" t="s" s="2">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="L93" s="2"/>
       <c r="M93" s="2"/>
@@ -10833,7 +10829,7 @@
         <v>74</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>80</v>
@@ -10853,10 +10849,10 @@
     </row>
     <row r="94">
       <c r="A94" t="s" s="2">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
@@ -10932,7 +10928,7 @@
         <v>74</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>75</v>

--- a/htr-FHIR/ig/StructureDefinition-fr-core-service-event.xlsx
+++ b/htr-FHIR/ig/StructureDefinition-fr-core-service-event.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-24T13:32:36+00:00</t>
+    <t>2025-02-24T13:36:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/htr-FHIR/ig/StructureDefinition-fr-core-service-event.xlsx
+++ b/htr-FHIR/ig/StructureDefinition-fr-core-service-event.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-24T13:36:50+00:00</t>
+    <t>2025-03-04T16:07:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -449,7 +449,7 @@
 - Pour un document au format CDA R2 N3, se reporter au volet de contenus correspondant.
 - Pour certains documents au format CDA R2 N1, la valeur est fixée (voir tableau qui suit).
 - Dans les autres cas, utiliser une valeur issue d'une terminologie internationale (ex : CIM10 pour les actes) ou nationale (ex : CCAM pour les actes).
-Pour les documents d’expression personnelle du patient/usager :
+- Pour les documents d’expression personnelle du patient/usager :
 - valeur fixée</t>
   </si>
   <si>

--- a/htr-FHIR/ig/StructureDefinition-fr-core-service-event.xlsx
+++ b/htr-FHIR/ig/StructureDefinition-fr-core-service-event.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-04T16:07:16+00:00</t>
+    <t>2025-03-06T10:23:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/htr-FHIR/ig/StructureDefinition-fr-core-service-event.xlsx
+++ b/htr-FHIR/ig/StructureDefinition-fr-core-service-event.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-06T10:23:19+00:00</t>
+    <t>2025-03-10T13:00:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/htr-FHIR/ig/StructureDefinition-fr-core-service-event.xlsx
+++ b/htr-FHIR/ig/StructureDefinition-fr-core-service-event.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-10T13:00:25+00:00</t>
+    <t>2025-03-11T15:29:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/htr-FHIR/ig/StructureDefinition-fr-core-service-event.xlsx
+++ b/htr-FHIR/ig/StructureDefinition-fr-core-service-event.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-11T15:29:00+00:00</t>
+    <t>2025-03-12T13:18:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/htr-FHIR/ig/StructureDefinition-fr-core-service-event.xlsx
+++ b/htr-FHIR/ig/StructureDefinition-fr-core-service-event.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-12T13:18:22+00:00</t>
+    <t>2025-03-14T15:47:10+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/htr-FHIR/ig/StructureDefinition-fr-core-service-event.xlsx
+++ b/htr-FHIR/ig/StructureDefinition-fr-core-service-event.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-14T15:47:10+00:00</t>
+    <t>2025-03-25T13:52:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/htr-FHIR/ig/StructureDefinition-fr-core-service-event.xlsx
+++ b/htr-FHIR/ig/StructureDefinition-fr-core-service-event.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-25T13:52:25+00:00</t>
+    <t>2025-03-25T14:07:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/htr-FHIR/ig/StructureDefinition-fr-core-service-event.xlsx
+++ b/htr-FHIR/ig/StructureDefinition-fr-core-service-event.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-25T14:07:20+00:00</t>
+    <t>2025-03-31T09:17:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/htr-FHIR/ig/StructureDefinition-fr-core-service-event.xlsx
+++ b/htr-FHIR/ig/StructureDefinition-fr-core-service-event.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-31T09:17:15+00:00</t>
+    <t>2025-04-14T15:21:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/htr-FHIR/ig/StructureDefinition-fr-core-service-event.xlsx
+++ b/htr-FHIR/ig/StructureDefinition-fr-core-service-event.xlsx
@@ -42,7 +42,7 @@
     <t>Title</t>
   </si>
   <si>
-    <t>serviceEvent</t>
+    <t>CDA - serviceEvent</t>
   </si>
   <si>
     <t>Status</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-04-14T15:21:44+00:00</t>
+    <t>2025-04-23T09:31:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1320,42 +1320,42 @@
   <dimension ref="A1:AK94"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="66.546875" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="66.546875" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="12.66015625" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="4" max="4" width="8.95703125" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="5" max="5" width="24.9375" customWidth="true" bestFit="true"/>
-    <col min="6" max="6" width="4.9453125" customWidth="true" bestFit="true"/>
-    <col min="7" max="7" width="5.4296875" customWidth="true" bestFit="true"/>
-    <col min="8" max="8" width="16.27734375" customWidth="true" bestFit="true"/>
-    <col min="9" max="9" width="13.26171875" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="57.05078125" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="57.05078125" customWidth="true" bestFit="true"/>
+    <col min="3" max="3" width="10.8515625" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="4" max="4" width="7.6796875" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="5" max="5" width="21.37890625" customWidth="true" bestFit="true"/>
+    <col min="6" max="6" width="4.23828125" customWidth="true" bestFit="true"/>
+    <col min="7" max="7" width="4.65625" customWidth="true" bestFit="true"/>
+    <col min="8" max="8" width="13.953125" customWidth="true" bestFit="true"/>
+    <col min="9" max="9" width="11.3671875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="151.96875" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="130.28515625" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
-    <col min="15" max="15" width="15.6640625" customWidth="true" bestFit="true"/>
+    <col min="15" max="15" width="13.4296875" customWidth="true" bestFit="true"/>
     <col min="16" max="16" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="17" max="17" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="18" max="18" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="19" max="19" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="20" max="20" width="9.953125" customWidth="true" bestFit="true"/>
-    <col min="21" max="21" width="17.171875" customWidth="true" bestFit="true"/>
-    <col min="22" max="22" width="17.65625" customWidth="true" bestFit="true"/>
-    <col min="23" max="23" width="19.03515625" customWidth="true" bestFit="true"/>
-    <col min="24" max="24" width="18.859375" customWidth="true" bestFit="true"/>
-    <col min="25" max="25" width="21.57421875" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="97.74609375" customWidth="true" bestFit="true"/>
-    <col min="27" max="27" width="6.34765625" customWidth="true" bestFit="true"/>
-    <col min="28" max="28" width="22.71875" customWidth="true" bestFit="true"/>
-    <col min="29" max="29" width="20.59375" customWidth="true" bestFit="true"/>
-    <col min="30" max="30" width="17.21484375" customWidth="true" bestFit="true"/>
-    <col min="31" max="31" width="14.4140625" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="32" max="32" width="38.20703125" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="33" max="33" width="10.5546875" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="34" max="34" width="11.0390625" customWidth="true" bestFit="true"/>
+    <col min="20" max="20" width="8.53515625" customWidth="true" bestFit="true"/>
+    <col min="21" max="21" width="14.72265625" customWidth="true" bestFit="true"/>
+    <col min="22" max="22" width="15.13671875" customWidth="true" bestFit="true"/>
+    <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
+    <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
+    <col min="25" max="25" width="18.49609375" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="83.80078125" customWidth="true" bestFit="true"/>
+    <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
+    <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
+    <col min="29" max="29" width="17.65625" customWidth="true" bestFit="true"/>
+    <col min="30" max="30" width="14.7578125" customWidth="true" bestFit="true"/>
+    <col min="31" max="31" width="12.359375" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="32" max="32" width="32.75390625" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="33" max="33" width="9.046875" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="34" max="34" width="9.46484375" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
-    <col min="37" max="37" width="24.98046875" customWidth="true" bestFit="true"/>
+    <col min="37" max="37" width="21.4140625" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
     <row r="1">

--- a/htr-FHIR/ig/StructureDefinition-fr-core-service-event.xlsx
+++ b/htr-FHIR/ig/StructureDefinition-fr-core-service-event.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-04-23T09:31:53+00:00</t>
+    <t>2025-04-24T14:52:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/htr-FHIR/ig/StructureDefinition-fr-core-service-event.xlsx
+++ b/htr-FHIR/ig/StructureDefinition-fr-core-service-event.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-04-24T14:52:25+00:00</t>
+    <t>2025-04-28T07:47:42+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/htr-FHIR/ig/StructureDefinition-fr-core-service-event.xlsx
+++ b/htr-FHIR/ig/StructureDefinition-fr-core-service-event.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-04-28T07:47:42+00:00</t>
+    <t>2025-04-28T07:48:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/htr-FHIR/ig/StructureDefinition-fr-core-service-event.xlsx
+++ b/htr-FHIR/ig/StructureDefinition-fr-core-service-event.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-04-28T07:48:19+00:00</t>
+    <t>2025-04-28T09:06:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/htr-FHIR/ig/StructureDefinition-fr-core-service-event.xlsx
+++ b/htr-FHIR/ig/StructureDefinition-fr-core-service-event.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-04-28T09:06:14+00:00</t>
+    <t>2025-04-28T09:53:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/htr-FHIR/ig/StructureDefinition-fr-core-service-event.xlsx
+++ b/htr-FHIR/ig/StructureDefinition-fr-core-service-event.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-04-28T09:53:39+00:00</t>
+    <t>2025-05-06T15:44:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/htr-FHIR/ig/StructureDefinition-fr-core-service-event.xlsx
+++ b/htr-FHIR/ig/StructureDefinition-fr-core-service-event.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-06T15:44:46+00:00</t>
+    <t>2025-05-06T15:53:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/htr-FHIR/ig/StructureDefinition-fr-core-service-event.xlsx
+++ b/htr-FHIR/ig/StructureDefinition-fr-core-service-event.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-06T15:53:54+00:00</t>
+    <t>2025-05-06T15:58:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/htr-FHIR/ig/StructureDefinition-fr-core-service-event.xlsx
+++ b/htr-FHIR/ig/StructureDefinition-fr-core-service-event.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-06T15:58:22+00:00</t>
+    <t>2025-05-20T10:20:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/htr-FHIR/ig/StructureDefinition-fr-core-service-event.xlsx
+++ b/htr-FHIR/ig/StructureDefinition-fr-core-service-event.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-20T10:20:09+00:00</t>
+    <t>2025-05-20T12:44:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
